--- a/artfynd/A 417-2023 artfynd.xlsx
+++ b/artfynd/A 417-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,9 +802,145 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135606389</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56930</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lagåsamon, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>456975</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6473894</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tibro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tibro</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Svart.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ingemar Axelsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ingemar Axelsson, Mariann Axelsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135606389</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 417-2023 artfynd.xlsx
+++ b/artfynd/A 417-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,145 +802,9 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>135606389</v>
-      </c>
-      <c r="B3" t="n">
-        <v>56930</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>208260</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Vipera berus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Lagåsamon, Vg</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>456975</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6473894</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Tibro</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Tibro</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Svart.</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Ingemar Axelsson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Ingemar Axelsson, Mariann Axelsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135606389</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 417-2023 artfynd.xlsx
+++ b/artfynd/A 417-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,9 +802,145 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135606389</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56932</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lagåsamon, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>456975</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6473894</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tibro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tibro</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Svart.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ingemar Axelsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ingemar Axelsson, Mariann Axelsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135606389</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 417-2023 artfynd.xlsx
+++ b/artfynd/A 417-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,145 +802,9 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>135606389</v>
-      </c>
-      <c r="B3" t="n">
-        <v>56932</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>208260</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Huggorm</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Vipera berus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Lagåsamon, Vg</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>456975</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6473894</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Tibro</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Tibro</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Svart.</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Ingemar Axelsson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Ingemar Axelsson, Mariann Axelsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135606389</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 417-2023 artfynd.xlsx
+++ b/artfynd/A 417-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>135606389</v>
       </c>
       <c r="B3" t="n">
-        <v>56932</v>
+        <v>56933</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
